--- a/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/胆固醇磷硫铁法预实验.xlsx
+++ b/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/胆固醇磷硫铁法预实验.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11211"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peiyuliu/Desktop/PKU-Undergraduate-Course-Public/生物化学实验(Biochemistry Lab)/开放实验/开放实验酶标仪数据/磷硫铁法/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6EF51A0-2D2E-9F48-A443-D16467AE78AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="120" windowWidth="9435" windowHeight="6915"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="板 1 - Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,12 +19,46 @@
     <definedName name="MethodPointer1">578616160</definedName>
     <definedName name="MethodPointer2">334</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>软件版本</t>
   </si>
@@ -304,11 +344,14 @@
   <si>
     <t>H</t>
   </si>
+  <si>
+    <t>加样表：P66</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6">
     <font>
       <sz val="10"/>
@@ -434,7 +477,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -457,11 +500,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -517,17 +569,1000 @@
     <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="4.0901827334674646E-5"/>
+                  <c:y val="0.15770851996793814"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-CN"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'板 1 - Sheet1'!$P$34:$P$37</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'板 1 - Sheet1'!$Q$34:$Q$37</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5.5000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.4999999999999989E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.1000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.9999999999999923E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AE82-1240-835E-51CA208CA831}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="525478512"/>
+        <c:axId val="525500656"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="525478512"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="525500656"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="525500656"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="525478512"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD05CC05-6A19-394D-9BE0-DDC36819271E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -569,7 +1604,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -601,9 +1636,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -635,6 +1688,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -810,15 +1881,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:O32"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A2:AG69"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
+    <col min="20" max="20" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:20" ht="14">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -826,7 +1898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:20" ht="14">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -834,12 +1906,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:20" ht="14">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:20" ht="14">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -847,7 +1919,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:20" ht="14">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -855,7 +1927,7 @@
         <v>45611</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:20" ht="14">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -863,15 +1935,18 @@
         <v>0.73854166666666676</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:20" ht="14">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:2">
+      <c r="T9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="14">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -879,7 +1954,7 @@
         <v>19012425</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:20" ht="14">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -887,13 +1962,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:20" ht="14">
       <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="5"/>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:20" ht="14">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -901,12 +1976,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:20" ht="14">
       <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:20" ht="14">
       <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
@@ -914,28 +1989,28 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:33" ht="14">
       <c r="B17" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:33" ht="14">
       <c r="B18" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:33" ht="14">
       <c r="B19" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:33" ht="14">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="5"/>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:33" ht="14">
       <c r="A22" s="1" t="s">
         <v>24</v>
       </c>
@@ -943,7 +2018,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:33">
       <c r="B24" s="6"/>
       <c r="C24" s="7">
         <v>1</v>
@@ -982,7 +2057,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:33" ht="14">
       <c r="B25" s="7" t="s">
         <v>25</v>
       </c>
@@ -1025,8 +2100,15 @@
       <c r="O25" s="11">
         <v>560</v>
       </c>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="Q25">
+        <f t="shared" ref="Q25:Q39" si="0">R25 - 0.049</f>
+        <v>1.5000000000000013E-3</v>
+      </c>
+      <c r="R25">
+        <v>5.0500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33" ht="14">
       <c r="B26" s="7" t="s">
         <v>26</v>
       </c>
@@ -1066,11 +2148,21 @@
       <c r="N26" s="10">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="O26" s="11">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="O26" s="21">
+        <v>10</v>
+      </c>
+      <c r="P26">
+        <v>0.2</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="0"/>
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="R26">
+        <v>0.251</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33" ht="14">
       <c r="B27" s="7" t="s">
         <v>27</v>
       </c>
@@ -1110,11 +2202,67 @@
       <c r="N27" s="9">
         <v>5.5E-2</v>
       </c>
-      <c r="O27" s="11">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+      <c r="O27" s="21">
+        <v>9</v>
+      </c>
+      <c r="P27">
+        <v>0.18</v>
+      </c>
+      <c r="Q27">
+        <f t="shared" si="0"/>
+        <v>0.14150000000000001</v>
+      </c>
+      <c r="R27">
+        <v>0.1905</v>
+      </c>
+      <c r="S27" cm="1">
+        <f t="array" ref="S27:AG28">TRANSPOSE(P26:Q40)</f>
+        <v>0.2</v>
+      </c>
+      <c r="T27">
+        <v>0.18</v>
+      </c>
+      <c r="U27">
+        <v>0.16</v>
+      </c>
+      <c r="V27">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="W27">
+        <v>0.12</v>
+      </c>
+      <c r="X27">
+        <v>0.1</v>
+      </c>
+      <c r="Y27">
+        <v>0.08</v>
+      </c>
+      <c r="Z27">
+        <v>0.06</v>
+      </c>
+      <c r="AA27">
+        <v>0.04</v>
+      </c>
+      <c r="AB27">
+        <v>0.02</v>
+      </c>
+      <c r="AC27">
+        <v>0.01</v>
+      </c>
+      <c r="AD27">
+        <v>1E-3</v>
+      </c>
+      <c r="AE27">
+        <v>1E-4</v>
+      </c>
+      <c r="AF27">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33" ht="14">
       <c r="B28" s="7" t="s">
         <v>28</v>
       </c>
@@ -1154,11 +2302,66 @@
       <c r="N28" s="9">
         <v>5.5E-2</v>
       </c>
-      <c r="O28" s="11">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="O28" s="21">
+        <v>8</v>
+      </c>
+      <c r="P28">
+        <v>0.16</v>
+      </c>
+      <c r="Q28">
+        <f t="shared" si="0"/>
+        <v>0.13250000000000001</v>
+      </c>
+      <c r="R28">
+        <v>0.18149999999999999</v>
+      </c>
+      <c r="S28">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="T28">
+        <v>0.14150000000000001</v>
+      </c>
+      <c r="U28">
+        <v>0.13250000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0.13950000000000001</v>
+      </c>
+      <c r="W28">
+        <v>0.14800000000000002</v>
+      </c>
+      <c r="X28">
+        <v>8.5500000000000007E-2</v>
+      </c>
+      <c r="Y28">
+        <v>8.4500000000000006E-2</v>
+      </c>
+      <c r="Z28">
+        <v>5.1500000000000004E-2</v>
+      </c>
+      <c r="AA28">
+        <v>5.5000000000000007E-2</v>
+      </c>
+      <c r="AB28">
+        <v>3.4999999999999989E-2</v>
+      </c>
+      <c r="AC28">
+        <v>2.1000000000000005E-2</v>
+      </c>
+      <c r="AD28">
+        <v>6.9999999999999923E-3</v>
+      </c>
+      <c r="AE28">
+        <v>3.5000000000000031E-3</v>
+      </c>
+      <c r="AF28">
+        <v>1.9999999999999948E-3</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33" ht="14">
       <c r="B29" s="7" t="s">
         <v>29</v>
       </c>
@@ -1198,11 +2401,21 @@
       <c r="N29" s="9">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="O29" s="11">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
+      <c r="O29" s="21">
+        <v>7</v>
+      </c>
+      <c r="P29">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q29">
+        <f t="shared" si="0"/>
+        <v>0.13950000000000001</v>
+      </c>
+      <c r="R29">
+        <v>0.1885</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33" ht="14">
       <c r="B30" s="7" t="s">
         <v>30</v>
       </c>
@@ -1242,11 +2455,21 @@
       <c r="N30" s="9">
         <v>5.5E-2</v>
       </c>
-      <c r="O30" s="11">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
+      <c r="O30" s="21">
+        <v>6</v>
+      </c>
+      <c r="P30">
+        <v>0.12</v>
+      </c>
+      <c r="Q30">
+        <f t="shared" si="0"/>
+        <v>0.14800000000000002</v>
+      </c>
+      <c r="R30">
+        <v>0.19700000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33" ht="14">
       <c r="B31" s="7" t="s">
         <v>31</v>
       </c>
@@ -1286,11 +2509,21 @@
       <c r="N31" s="9">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="O31" s="11">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
+      <c r="O31" s="21">
+        <v>5</v>
+      </c>
+      <c r="P31">
+        <v>0.1</v>
+      </c>
+      <c r="Q31">
+        <f t="shared" si="0"/>
+        <v>8.5500000000000007E-2</v>
+      </c>
+      <c r="R31">
+        <v>0.13450000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" ht="14">
       <c r="B32" s="7" t="s">
         <v>32</v>
       </c>
@@ -1330,14 +2563,896 @@
       <c r="N32" s="9">
         <v>5.5E-2</v>
       </c>
-      <c r="O32" s="11">
-        <v>560</v>
+      <c r="O32" s="21">
+        <v>4</v>
+      </c>
+      <c r="P32">
+        <v>0.08</v>
+      </c>
+      <c r="Q32">
+        <f t="shared" si="0"/>
+        <v>8.4500000000000006E-2</v>
+      </c>
+      <c r="R32">
+        <v>0.13350000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="6:18">
+      <c r="O33">
+        <v>3</v>
+      </c>
+      <c r="P33">
+        <v>0.06</v>
+      </c>
+      <c r="Q33">
+        <f t="shared" si="0"/>
+        <v>5.1500000000000004E-2</v>
+      </c>
+      <c r="R33">
+        <v>0.10050000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="6:18">
+      <c r="O34">
+        <v>2</v>
+      </c>
+      <c r="P34">
+        <v>0.04</v>
+      </c>
+      <c r="Q34">
+        <f t="shared" si="0"/>
+        <v>5.5000000000000007E-2</v>
+      </c>
+      <c r="R34">
+        <v>0.10400000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="6:18">
+      <c r="O35">
+        <v>1</v>
+      </c>
+      <c r="P35">
+        <v>0.02</v>
+      </c>
+      <c r="Q35">
+        <f t="shared" si="0"/>
+        <v>3.4999999999999989E-2</v>
+      </c>
+      <c r="R35">
+        <v>8.3999999999999991E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="6:18">
+      <c r="O36">
+        <v>0.5</v>
+      </c>
+      <c r="P36">
+        <v>0.01</v>
+      </c>
+      <c r="Q36">
+        <f t="shared" si="0"/>
+        <v>2.1000000000000005E-2</v>
+      </c>
+      <c r="R36">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="6:18">
+      <c r="O37">
+        <v>0.05</v>
+      </c>
+      <c r="P37">
+        <v>1E-3</v>
+      </c>
+      <c r="Q37">
+        <f t="shared" si="0"/>
+        <v>6.9999999999999923E-3</v>
+      </c>
+      <c r="R37">
+        <v>5.5999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="6:18">
+      <c r="O38">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="P38">
+        <v>1E-4</v>
+      </c>
+      <c r="Q38">
+        <f t="shared" si="0"/>
+        <v>3.5000000000000031E-3</v>
+      </c>
+      <c r="R38">
+        <v>5.2500000000000005E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="6:18">
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+      <c r="H39">
+        <v>3</v>
+      </c>
+      <c r="I39">
+        <v>4</v>
+      </c>
+      <c r="J39">
+        <v>5</v>
+      </c>
+      <c r="K39">
+        <v>6</v>
+      </c>
+      <c r="L39">
+        <v>7</v>
+      </c>
+      <c r="M39">
+        <v>8</v>
+      </c>
+      <c r="O39">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="P39">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Q39">
+        <f t="shared" si="0"/>
+        <v>1.9999999999999948E-3</v>
+      </c>
+      <c r="R39">
+        <v>5.0999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="6:18">
+      <c r="F40" cm="1">
+        <f t="array" ref="F40:M51">TRANSPOSE(C25:N32)</f>
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="G40">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="H40">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="I40">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="J40">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="K40">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="L40">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="M40">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <f>R40 - 0.049</f>
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>4.9000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="6:18">
+      <c r="F41">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="G41">
+        <v>0.123</v>
+      </c>
+      <c r="H41">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="I41">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="J41">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="K41">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="L41">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="M41">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="42" spans="6:18">
+      <c r="F42">
+        <v>0.05</v>
+      </c>
+      <c r="G42">
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="H42">
+        <v>0.115</v>
+      </c>
+      <c r="I42">
+        <v>0.15</v>
+      </c>
+      <c r="J42">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="K42">
+        <v>0.223</v>
+      </c>
+      <c r="L42">
+        <v>0.15</v>
+      </c>
+      <c r="M42">
+        <v>0.13300000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="6:18">
+      <c r="F43">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="G43">
+        <v>0.246</v>
+      </c>
+      <c r="H43">
+        <v>0.26600000000000001</v>
+      </c>
+      <c r="I43">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="J43">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="K43">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="L43">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="M43">
+        <v>0.13400000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="6:18">
+      <c r="F44">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="G44">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="H44">
+        <v>0.05</v>
+      </c>
+      <c r="I44">
+        <v>6.3E-2</v>
+      </c>
+      <c r="J44">
+        <v>6.2E-2</v>
+      </c>
+      <c r="K44">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="L44">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="M44">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="P44">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="45" spans="6:18">
+      <c r="F45">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="G45">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="H45">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="I45">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="J45">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="K45">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="L45">
+        <v>0.05</v>
+      </c>
+      <c r="M45">
+        <v>0.05</v>
+      </c>
+      <c r="P45">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="46" spans="6:18">
+      <c r="F46">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="G46">
+        <v>4.7E-2</v>
+      </c>
+      <c r="H46">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="I46">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="J46">
+        <v>0.05</v>
+      </c>
+      <c r="K46">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="L46">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="M46">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="P46">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="47" spans="6:18">
+      <c r="F47">
+        <v>0.05</v>
+      </c>
+      <c r="G47">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="H47">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="I47">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="J47">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="K47">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="L47">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="M47">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="P47">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="6:18">
+      <c r="F48">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="G48">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="H48">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="I48">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="J48">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="K48">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="L48">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="M48">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="P48">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="49" spans="6:23">
+      <c r="F49">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="G49">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="H49">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="I49">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="J49">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="K49">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="L49">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="M49">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="P49">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="50" spans="6:23">
+      <c r="F50">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="G50">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="H50">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="I50">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="J50">
+        <v>0.05</v>
+      </c>
+      <c r="K50">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="L50">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="M50">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="P50">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="51" spans="6:23">
+      <c r="F51">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="G51">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="H51">
+        <v>5.5E-2</v>
+      </c>
+      <c r="I51">
+        <v>5.5E-2</v>
+      </c>
+      <c r="J51">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="K51">
+        <v>5.5E-2</v>
+      </c>
+      <c r="L51">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="M51">
+        <v>5.5E-2</v>
+      </c>
+      <c r="P51">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="52" spans="6:23">
+      <c r="P52">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="53" spans="6:23">
+      <c r="P53">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="54" spans="6:23">
+      <c r="P54">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="55" spans="6:23">
+      <c r="P55">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="6:23">
+      <c r="P56">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="57" spans="6:23">
+      <c r="F57">
+        <v>8</v>
+      </c>
+      <c r="G57">
+        <v>7</v>
+      </c>
+      <c r="H57">
+        <v>6</v>
+      </c>
+      <c r="I57">
+        <v>5</v>
+      </c>
+      <c r="J57">
+        <v>4</v>
+      </c>
+      <c r="K57">
+        <v>3</v>
+      </c>
+      <c r="L57">
+        <v>2</v>
+      </c>
+      <c r="M57">
+        <v>1</v>
+      </c>
+      <c r="P57">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="58" spans="6:23">
+      <c r="P58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="6:23">
+      <c r="F62">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="G62">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="H62">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="I62">
+        <v>6.2E-2</v>
+      </c>
+      <c r="J62">
+        <v>6.3E-2</v>
+      </c>
+      <c r="K62">
+        <v>0.05</v>
+      </c>
+      <c r="L62">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="M62">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="P62">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="Q62">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="R62">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="S62">
+        <v>0.05</v>
+      </c>
+      <c r="T62">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="U62">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="V62">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="W62">
+        <v>5.0999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="6:23">
+      <c r="F63">
+        <v>0.05</v>
+      </c>
+      <c r="G63">
+        <v>0.05</v>
+      </c>
+      <c r="H63">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="I63">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="J63">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="K63">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="L63">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="M63">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="P63">
+        <v>5.5E-2</v>
+      </c>
+      <c r="Q63">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="R63">
+        <v>5.5E-2</v>
+      </c>
+      <c r="S63">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="T63">
+        <v>5.5E-2</v>
+      </c>
+      <c r="U63">
+        <v>5.5E-2</v>
+      </c>
+      <c r="V63">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="W63">
+        <v>6.6000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="6:23">
+      <c r="F64">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="G64">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="H64">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="I64">
+        <v>0.05</v>
+      </c>
+      <c r="J64">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="K64">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="L64">
+        <v>4.7E-2</v>
+      </c>
+      <c r="M64">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="P64">
+        <f>(P62+P63)/2</f>
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="Q64">
+        <f t="shared" ref="Q64:W64" si="1">(Q62+Q63)/2</f>
+        <v>5.1499999999999997E-2</v>
+      </c>
+      <c r="R64">
+        <f t="shared" si="1"/>
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="S64">
+        <f t="shared" si="1"/>
+        <v>5.3000000000000005E-2</v>
+      </c>
+      <c r="T64">
+        <f t="shared" si="1"/>
+        <v>5.3499999999999999E-2</v>
+      </c>
+      <c r="U64">
+        <f t="shared" si="1"/>
+        <v>5.0500000000000003E-2</v>
+      </c>
+      <c r="V64">
+        <f t="shared" si="1"/>
+        <v>6.2E-2</v>
+      </c>
+      <c r="W64">
+        <f t="shared" si="1"/>
+        <v>5.8499999999999996E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="6:23">
+      <c r="F65">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="G65">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="H65">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="I65">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="J65">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="K65">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="L65">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="M65">
+        <v>0.05</v>
+      </c>
+      <c r="P65">
+        <f>ABS(P63-P62)</f>
+        <v>4.0000000000000036E-3</v>
+      </c>
+      <c r="Q65">
+        <f t="shared" ref="Q65:W65" si="2">ABS(Q63-Q62)</f>
+        <v>1.0000000000000009E-3</v>
+      </c>
+      <c r="R65">
+        <f t="shared" si="2"/>
+        <v>4.0000000000000036E-3</v>
+      </c>
+      <c r="S65">
+        <f t="shared" si="2"/>
+        <v>5.9999999999999984E-3</v>
+      </c>
+      <c r="T65">
+        <f t="shared" si="2"/>
+        <v>3.0000000000000027E-3</v>
+      </c>
+      <c r="U65">
+        <f t="shared" si="2"/>
+        <v>9.0000000000000011E-3</v>
+      </c>
+      <c r="V65">
+        <f t="shared" si="2"/>
+        <v>2.7999999999999997E-2</v>
+      </c>
+      <c r="W65">
+        <f t="shared" si="2"/>
+        <v>1.5000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="6:23">
+      <c r="F66">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="G66">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="H66">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="I66">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="J66">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="K66">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="L66">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="M66">
+        <v>4.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="6:23">
+      <c r="F67">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="G67">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="H67">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="I67">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="J67">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="K67">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="L67">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="M67">
+        <v>4.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="6:23">
+      <c r="F68">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="G68">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="H68">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="I68">
+        <v>0.05</v>
+      </c>
+      <c r="J68">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="K68">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="L68">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="M68">
+        <v>5.0999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="6:23">
+      <c r="F69">
+        <v>5.5E-2</v>
+      </c>
+      <c r="G69">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="H69">
+        <v>5.5E-2</v>
+      </c>
+      <c r="I69">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="J69">
+        <v>5.5E-2</v>
+      </c>
+      <c r="K69">
+        <v>5.5E-2</v>
+      </c>
+      <c r="L69">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="M69">
+        <v>6.6000000000000003E-2</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="F57:M69">
+    <sortCondition descending="1" ref="F57:M57"/>
+  </sortState>
   <phoneticPr fontId="0" type="noConversion"/>
+  <conditionalFormatting sqref="F40:M51">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color theme="3"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="256" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>